--- a/global_startups_final.xlsx
+++ b/global_startups_final.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Singapore" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shanghai" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tokyo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paris" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tel Aviv'!$A$1:$J$170</definedName>
@@ -21,6 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Singapore'!$A$1:$J$242</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Shanghai'!$A$1:$J$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tokyo'!$A$1:$J$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Paris'!$A$1:$J$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53943,4 +53945,8195 @@
   <autoFilter ref="A1:J163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J157"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last Round</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Founders</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Top Investors</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Team Size</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Software as a service (SaaS), Machine learning, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mistral AI is an AI-driven LLMs platform founded in 2023 by Arthur Mensch, Timothée Lacroix and Guillaume Lample.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>€2.8B</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Mensch, Charles Gorintin, Guillaume Lample, Jean Charles Samuelian, Timothee Lacroix</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Andreessen Horowitz, General Catalyst, NVIDIA, Bpifrance, Lightspeed Venture Partners</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Large Team (251-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EcoVadis</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Business intelligence (BI), Supply chain, Financial technology</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Ecovadis is an environmental sustainability ratings platform to assess corporate social responsibility and sustainable procurement.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>$735.8M</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Secondary Market</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Frederic Trinel, Pierre Francois Thaler</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>BlackRock, General Atlantic, CVC Capital Partners, Astorg, Partech</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Major Organization (1,001-5,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Qovery</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>$17.1M</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Morgan Perry, Pierre Mavro, Romaric Philogene</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Techstars, Speedinvest, Crane Venture Partners, IRIS, Founders Future</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Lean Team (11-50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Finary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>€37.4M</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Julien Blancher, Mounir Laggoune</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>LocalGlobe, Speedinvest, Y Combinator, Crowdcube, Kima Ventures</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Founding Team (1-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Genomines</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>$61.8M</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Dali Rashid, Fabien Koutchekian</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Bpifrance, Entrepreneurs First, Lowercarbon Capital, Elemental Impact, Engine Ventures</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Lean Team (11-50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Bioptimus</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>$76M</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>David Cahané, Eric Durand, Felipe Llinares López, Jean-Philippe Vert, Rodolphe Jenatton, Zelda Mariet</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Bpifrance, Headline, Hitachi Ventures, Hummingbird Ventures, Cathay Innovation</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Founding Team (1-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Alice &amp; Bob</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Technology, Quantum computing, Manufacturing</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Alice &amp; Bob is an universal fault-tolerant quantum computer creator founded in 2020 by Théau Péronnin.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>$162.6M</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Raphaël Lescanne, Théau Péronnin</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Bpifrance, AVP, European Innovation Council, Supernova Invest, Acequia Capital (AceCap)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SafeHeal</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>$91M</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Anne Osdoit</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Sofinnova Partners, Asabys Partners, Genesis Medtech, Gideon Strategic Partners, M&amp;L Healthcare Investments</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Lean Team (11-50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>H Company</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>$220M</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Convertible Note</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Charles A. Kantor, Julien Perolat, Karl Tuyls</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Accel, Creandum, Amazon, FirstMark, UiPath</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Request Finance</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>$5.5M</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Adam Dowson, Christophe Lassuyt, Julien Devoir, Yoann Marion</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Bpifrance, Balderton Capital, XAnge, Animoca Brands, Sebastien Borget</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Lean Team (11-50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Defacto</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getdefacto.com/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>DeFacto is a Turkish brand of men's and women's clothing and accessories.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>$214M</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Marc-Henri Gires</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>WAAT</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>https://waat.fr/</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>$130M</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>UNIVITY</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.constellation.global/</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>$40.3M</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Alpic</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>https://alpic.ai/</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>$6M</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Seed</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Vestiaire Collective</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>http://vestiairecollective.com/</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>$722.3M</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Equity Crowdfunding</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Nabla</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nabla.com/</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>$114.7M</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Scality</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>http://scality.com/</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>$172M</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Series E</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>HR Path</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>http://www.hr-path.com/en</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>$973M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Mobilize Financial Services</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://mobilize-fs.com/</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>$3.4B</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Goodvest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>https://goodvest.fr/</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>$23.9M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Shippeo</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>http://www.shippeo.com/</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>$137.8M</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Versant</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>https://versant.earth/</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>$640k</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Seed</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Devialet</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.devialet.com/en-eu/</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>$226.9M</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>GitGuardian</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gitguardian.com/</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>$56M</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Dust</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://dust.tt/</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Dust is a French artificial intelligence start-up using large language models (LLMs) on internal company data to improve productivity.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>$20M</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Akur8</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>http://www.akur8.com/</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Akur8 is an insurance company offering multiple coverages, including life, health, P&amp;C, and home insurance.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>$166.6M</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Guillaume Beraud-Sudreau</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Dotfile</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dotfile.com/</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>$8.5M</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Kiln</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.kiln.fi/</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Kiln is an entreprise-grade staking platform.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>$39.6M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AB Tasty</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>http://www.abtasty.com/</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>$65.7M</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Doctolib</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>http://www.doctolib.fr/</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>$815M</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Series F</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Newcleo</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.newcleo.com/</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>$677.1M</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Flowdesk</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>https://flowdesk.co/</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>$282M</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Christian Louboutin</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>http://us.christianlouboutin.com/ot_en/</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>$541M</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Bubblemaps</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>https://bubblemaps.io/</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>$4M</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Initial Coin Offering</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>http://www.psg.fr/</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>$531.3M</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Secondary Market</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Morpho Labs</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>https://morpho.org/</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>$68M</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Vocca</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://vocca.ai/</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>$5.5M</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Malt</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.malt.com/</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>$195.3M</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Wandercraft</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>http://www.wandercraft.eu/</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>$170.6M</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>JUISCI</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.juisci.com/</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>$6.7M</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>$87.4M</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Exail Technologies</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.exail-technologies.com/</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>$300M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Vizzia</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vizzia.fr/</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>$19.4M</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Nucleon Security</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>https://nucleon-security.com/en</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>$3M</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Swan</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>https://swan.io/</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>$100M</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Mediawan</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mediawan.com/</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>$725M</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Malou</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>https://malou.io/</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>$10M</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Retab</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.retab.com/</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>$7M</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Seed</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Pennylane</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pennylane.com/</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Provider of financial OS for European SMEs.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>$213.5M</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Edourd mascre **@pennylane.com</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Filigran</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>https://filigran.io/</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>$52.3M</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Prophesee</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prophesee.ai/</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>$105M</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Back Market</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>https://www.backmarket.com/</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Back Market is an online refurbished goods marketplace connecting consumers with sellers of electronic devices.</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>$1B</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Series E</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Greenway</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greenway.care/</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>$32M</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Inato</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>https://inato.com/</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Inato matches the right sites to the right clinical research study, globally.</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>$35.5M</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Philippe Ravaud</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Zefir</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zefir.fr/</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>$50M</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Dfns</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dfns.co/</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>$30.6M</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Kayrros</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kayrros.com/</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>$78.6M</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>ArcaScience</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.arcascience.ai/</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>$6M</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Alltheway</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alltheway.io/</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>LumApps</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>http://www.lumapps.com/</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>$102M</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Spiko</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.spiko.io/</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>$22.5M</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>BeReal.</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>https://bereal.com/</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>BeReal is social media platform that prompts users to take one photo each day at a random time.</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>$90M</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Alexis Barreyat</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Rippletide</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>https://rippletide.com/</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>$4M</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Amplitude Studios</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>https://www.amplitude-studios.com/</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>$12M</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Edflex</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edflex.com/</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>$37.1M</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Yubo</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>http://www.yubo.live/</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>$65.7M</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Animaj</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.animaj.com/</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>$175M</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Cycle App</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>https://cycle.app/</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>$6M</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Veesion</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>http://veesion.io/</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>$71M</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Stoïk</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>https://stoik.com/</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>$49.8M</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Fabriq</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fabriq.tech/</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>$29.9M</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Naboo</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>https://naboo.app/</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>$29.5M</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>https://escape.tech/</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>$6M</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Greenly</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>https://www.greenly.earth/home</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>$78M</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Chipiron</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chipiron.co/</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>$25.8M</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Platform.sh</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>https://platform.sh/</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>$187.3M</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Kaiko</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>http://www.kaiko.com/</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>$82.5M</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Kestra Technologies</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>https://kestra.io/</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>$11M</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>EndoGene.Bio</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>https://endogene.bio/</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>$2.9M</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Seed</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>ODDO BHF</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>http://www.oddo-bhf.com/</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Lydia</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>https://lydia-app.com/</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>$259.6M</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Surfe</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.surfe.com/</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>$4M</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Corwave</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.corwave.com/</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>$112.2M</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>73 Strings</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>https://www.73strings.com/</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>73 Strings is an AI-powered financial intelligence platform founded in 2019 by Sambeet Parija, Abhishek Pandey, Vinod Vijapur and Yann Magnan.</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>$65.1M</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Sifflet</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.siffletdata.com/</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>$35.8M</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Dental Monitoring</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>http://dental-monitoring.com/</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>$232.4M</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Mirakl</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>http://www.mirakl.com/</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Mirakl is a Paris, France-based company offering software solutions for e-commerce marketplace companies.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>$1.1B</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ManoMano</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>http://www.manomano.fr/</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>$705.5M</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Series F</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Pivot</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pivotapp.ai/</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>$25M</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Maki</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.makipeople.com/</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>$37M</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Flagcat</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>https://flagcat.studio/</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>€4.5M</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Bling</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bling.eu/</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>$6.7M</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Allianz Trade</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allianz-trade.com/</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>InsurTech</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Trezy</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>https://trezy.io/</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>$4M</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Hopia</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>https://hopia.eu/</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>$3.5M</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Mitrust</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>https://m-itrust.com/</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>$5M</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Qynapse</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>http://www.qynapse.com/</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>$6.6M</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>FinFrog</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>https://finfrog.fr/</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>$20.1M</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Prove &amp; Run</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>http://www.provenrun.com/</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>$15M</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Sarus</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>https://sarus.tech/</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>$2.7M</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Hugging Face</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI), Natural language processing (NLP), Machine learning</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Hugging Face is an open-source hosting platform for natural language processing and machine learning domains, such as computer vision and reinforcement learning, and for developing and deploying machine learning models for various applications.</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>$395.2M</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Coinhouse</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Financial technology, Cryptocurrency, Blockchain</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Coinhouse is the developer of an investment platform for cryptocurrency assets.</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>$110.1M</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Pasqal</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Energy industry, Manufacturing, Quantum computing</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Pasqal is a company building programmable quantum simulators and quantum computers made of 2D and 3D arrays of neutral atoms.</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>$140.5M</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Ledger (cryptocurrency wallet company)</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Blockchain, Cryptocurrency, Cryptocurrency wallet</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Hardware wallet for crypto assets such as Bitcoin, Ethereum, XRP, Monero and more.</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>$1.0B</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>Joel Pobeda, Nicolas Bacca</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Algolia</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Software as a service (SaaS), Application programming interface (API), Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Algolia is a company designing and building search and discovery API for websites and mobile apps. It participated in the W14 cohort of Y Combinator.</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>$462.2M</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Arianee</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Smart contract, Web3, Blockchain and cryptocurrency</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>The Arianee is a multichain token and protocol built on both the Ethereum core network and the Ethereum sidechain called POAnetwork.</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>$63.1M</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Frédéric Montagnon, Christian Jorge *@jorge.fr</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Massa</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Blockchain, Blockchain and cryptocurrency, Cryptocurrency</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Massa is a decentralized and scaled blockchain.</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>$5.7M</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Sébastien Forestier ***@forest.bio, Adrien Laversanne-Finot **@mit.edu</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Eleven Labs</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>E-commerce, Web development, Architecture</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>ElevenLabs is a voice artificial intelligence (AI) research and development company developing text-to-speech and voice cloning software.</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>$21.0M</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Quandela</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Metamaterial, Quantum sensor, Quantum communication</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Quandela is a Paris-based company developing optical quantum technology integrated into photonic chips.</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>$88.0M</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Shift Technology</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Software, Insurance, Big data</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>An insurance technology company offering artificially intelligent software for insurance fraud detection and claims handling.</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>$568.0M</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Telephony, Software, Small business</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Cloud based phone system and call center software with integrations into CRMs &amp; helpdesk software.</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>$383.4M</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Pierre-Baptiste Béchu **@aircall.io, Xavier Durand</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Online to offline, Sharing economy, Retail</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Storefront is a sharing-economy company that provides short-term retail spaces for rent to companies through an online platform, used specifically as pop-up retail locations.</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>$1.6M</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>Mohamed Haouache **@thestorefront.com, Erik Eliason</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Eligo Bioscience</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic biology, Therapeutics, Drug discovery</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Eligo Bioscience is a developer of novel genetic medicines founded in 2014 by Timothy Lu, Xavier Duportet, Luciano Marraffini and David Bikard.</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>$87.6M</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Timothy Lu ***.**@sentibio.com, Luciano Marraffini</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Financial technology, Technology, Health technology</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Alan is a digital health insurance provider for companies and freelancers.</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>$1.6B</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Jean-Charles Samuelian Werve</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ContentSquare</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Technology, Retail, Analytics</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>ContentSquare is an experience optimization platform for business that captures visitor behavior insights, designed to help increase conversions. It uses artificial intelligence to provide automatic recommendations.</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>$1.5B</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Gleamer</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Software engineering, Medical imaging, Radiology</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Gleamer is an AI solutions provider for radiology founded in 2017 by Nicolas COSME, Christian Allouche, Alexis Ducarouge and Nor-Eddine Regnard.</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>$168.6M</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>Nicolas COSME</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Ynsect</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Clean technology, Insect farming, Agricultural technology (AgTech)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Insect ingredient producer for animals, people, and plants.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>$393.3M</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Alexis Angot, Fabrice Berro</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Qonto</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Neobanking, Financial technology, Software as a service (SaaS)</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Qonto is a French online payment institution for freelancers and small and medium enterprises.</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>$687.3M</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>PhotoRoom</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Photography, Digital photography, Photo editing</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>PhotoRoom is a French company that provides photo editing software via an AI-powered photo editor.</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>$93.3M</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Actiondesk</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Technology, No-code / low-code development, Automation</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>A software company headquartered in San Francisco, California providing spreadsheet workflow automation software for businesses.</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>$7.9M</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Mailjet</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Technology, Application programming interface (API), Software as a service (SaaS)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Mailjet is an email services provider.</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>$17.6M</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Nicolas Chaunu</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Ankorstore</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>E-commerce, Application software, Information technology</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace connecting independent shop owners and brands with local retailers.</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>$544.0M</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>DNA Script</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Genetics, Genomics, Biomedical engineering</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>DNA Script is a DNA synthesis company founded by Thomas Ybert, Sylvain Gariel, and Xavier Gordon in 2014, and headquartered in Paris, France.</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>$427.1M</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>ClipDrop</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Computer Vision, Generative AI</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>ClipDrop is an application developed to turn mobile photons into professional product visuals. The application and the company behind it were acquired by Stability AI in 2023.</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>$1.7M</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Le Wagon</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Training, Educational Technology, Education</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Le Wagon runs immersive coding bootcamps in 44 campuses worldwide.</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>$19.0M</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Fernando Americano, Sébastien Saunier</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>FairMoney</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Financial technology, Financial services, Microcredit</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>FairMoney is a Paris-based start-up which offers micro loans in Nigeria through their mobile, Android app.</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>$64.0M</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>Matthieu Gendreau</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>HighRadius</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI), Computer Software, Automation</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Receivables and Treasury cloud software, powered by AI to optimize working capital.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>$475.0M</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Luko</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Insurance, Technology, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Luko is a home insurance company that uses technology to streamline the process of getting home insurance and making claims. It is located in Paris, France and was founded in 2016.</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>$152.6M</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>Raphaël Vullierme</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Slite</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge management (KM), Productivity software, Software as a service (SaaS)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Slite is an information organizing platform for corporate teams, for the purpose of collaborative productivity.</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>$26.4M</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Thibaud Elziere</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Viadeo</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Social networking service, Social network, Social media</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Viadeo is a social networking service founded in 2004 by Dan Serfaty.</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>$84.4M</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>Dan Serfaty</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Fairlyne</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Software as a service (SaaS), Hospitality industry, Travel technology</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Fairlyne is a resale-as-a-service platform offering incremental revenue to the travel industry.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>$6.0M</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Aqemia</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI), Biopharmaceutical, Technology</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>AI-powered drug discovery platform.</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>$76.9M</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Maximilien Leveque **@aqemia.com</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>OpenWeb</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Marketing, Chat (industry), Social media</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>OpenWeb, previously known as Spot.IM, is a conversation platform intended for publishers to start meaningful user discussions.</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>$383.0M</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Nadav Shoval, Roee Goldberg, Ishay Green</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Livestorm</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Sales and Marketing, Video, Software</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>A software company offering a video conferencing platform for webinars and video meetings.</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>$70.2M</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Ikonisys</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Medical diagnostics, Biomedical engineering, Engineering</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>A medical diagnostic products company focused on the diagnosis of cancers</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>$1.4M</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Michael W Kilpatrick, PhD, Achraf Hakimi Twitter, Aqil Mammadov</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Starburst</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Knowledge management (KM), Analytics, Enterprise software</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>An enterprise software company offering a platform for SQL analytics.</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>$414.0M</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>David Phillips</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Homa Games</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Cryptocurrency, Blockchain, Gaming</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Homa Games is a digital tools for mobile games developers founded in 2018.</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>$195.0M</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Hootsuite</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Software, Productivity software, Social media</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Hootsuite is a social network management platform created to interact, listen and analyze results.</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>$99.3M</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Enterome</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Drug discovery, Medical diagnostics, Biomedical engineering</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Developer of OncoMimics™ immunotherapy to treat follicular lymphoma.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>$351.5M</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>NewsCatcher</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Business intelligence (BI), Analytics, Natural language processing (NLP)</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>NewsCatcher is a developer of a data scraping and crawling API that helps enterprises get instant access to news and events.</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>$500.0K</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Capsule Social</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Cryptocurrency, Blockchain, Blockchain and cryptocurrency</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Capsule Social is a decentralized publishing platform where writers can share their stories and knowledge without compromising their integrity.</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>$1.5M</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Nadim Kobeissi</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Spendesk</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Software, Finance, Small- and medium-sized enterprises</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Spendesk offers an all-in-one spend management platform for finance teams.</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>$524.9M</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>Thibaud Elziere (entrepreneur)</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Lemon Way</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Crowdfunding, Financial services, Finance</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>A financial technology company offering payment solutions for e-commerce websites, crowdfunding platforms, and online marketplaces.</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>$25.5M</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Montalban, Sébastien Burlet</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Dawex</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Big data, Finance, Trade</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>A data marketplace for B2B sharing, acquiring, and monetizing data.</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>$11.6M</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Aplo</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Cryptocurrency, Finance, Technology</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Aplo (formerly SheeldMarket) is a cryptocurrency broker.</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>$11.0M</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Jacques Lolieux</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>LocoNav</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Software, Fleet management</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>A software company offering a platform for vehicle fleet management intelligent analytics and the internet of things (IoT).</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>$84.1M</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Clustree</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Consulting industry, Software as a service (SaaS), Analytics</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Clustree is an automated HR recommendation platform.</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Bénédicte de Raphélis Soissan</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Coave Therapeutics</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Deep Tech, Tissue engineering, Health technology</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Coave Therapeutics is a genetic medicines developer founded in 2014.</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>$94.2M</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Flowlity</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Supply chain, Business intelligence (BI), Technology</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>SaaS using AI to build resilient supply chain, predict sales and consumptions and optimize inventories</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>$6.6M</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Lago</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>No-code / low-code development, Software as a service (SaaS), Financial technology</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Lago is a Paris-based software company developing no-code tools for data teams.</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>$4.3M</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>JobTeaser</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Consulting industry, Recruitment, College recruiting</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>A software company that has created a mobile application that is a recruitment platform working with students, universities, and companies. It was founded in 2008 and is located in Paris, France.</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>$71.7M</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Expliseat</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Transportation, Aerospace, Manufacturing</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Expliseat is a manufacturer of ultra-light aircraft seats founded in 2011.</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>$41.0M</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>PayFit</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Employee benefits, Cloud computing, Software</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>PayFit is Europe's leading cloud-based and integrated payroll and HR software. We give you the visibility and automation you need to easily manage your payroll, with the support of payroll experts. With many businesses often choosing between in-house or outsourced payroll, PayFit looks to offer a hy...</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>$961.6M</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Actility</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Facility management, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Actility is a software company providing low power wide area (LoRaWAN and 3GPP connectivity) network connectivity management.</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>$106.8M</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Boris Dezier</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Dashlane</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Cloud computing security, Technology, Shopping</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Dashlane is a password manager software company founded by Emmanuel Schalit, Alexis Fogel, Guillaume Maron and Jean Guillou.</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>$274.5M</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Jean Guillou (entrepreneur) Twitter</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Talkwalker</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Social media, Cybersecurity, Analytics</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Talkwalker is a social media analytics and monitoring tool.</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>$9.5M</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>Thibaut Britz, Sign up to access our full database, Enter your email and get access to 71,000 + technology companies you can partner with.</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J157"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/global_startups_final.xlsx
+++ b/global_startups_final.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shanghai" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tokyo" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paris" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zurich" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tel Aviv'!$A$1:$J$170</definedName>
@@ -23,6 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Shanghai'!$A$1:$J$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tokyo'!$A$1:$J$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Paris'!$A$1:$J$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Zurich'!$A$1:$J$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62136,4 +62138,9204 @@
   <autoFilter ref="A1:J157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J176"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Last Round</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Founders</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Top Investors</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Team Size</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Drones, Robotics, Open-source software</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Auterion is a provider of autonomous systems software for defense founded in 2017 by Lorenz Meier.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>$181M</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Kevin Sartori, Lorenz Meier</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Bessemer Venture Partners, Lakestar, Costanoa Ventures, U.S. Department of Defense, Mosaic Ventures</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ANYbotics</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Automation, Robotics, Robot-enabled delivery</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>AI-driven robotic inspection solutions provider.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>$152.4M</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Andreas Lauber, Christian Gehring, Hanspeter Fässler, Marco Hutter, Peter Fankhauser</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Bessemer Venture Partners, NGP Capital, TDK Ventures, Verve Ventures, Supernova Invest</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Teylor</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Technology, Finance, Software as a service (SaaS)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Platform providing the fastest and most comfortable SME loans.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>$488.7M</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Staeuble</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Fasanara Capital, M&amp;G Plc, Barclays Investment Bank, WENVEST Capital, Weisshorn</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Climeworks</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Carbon capture and storage, Carbon offset, Direct air capture</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Climeworks is a direct Air Capture (DAC) technology developer founded in 2009 by Christoph Gebald.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>$946.1M</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Christoph Gebald, Jan Wurzbacher</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Partners Group, Zürcher Kantonal Bank, Baillie Gifford, GIC, Global Founders Capital</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Large Team (251-1,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Cutiss</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>$94.7M</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Daniela Marino, Fabienne Hartmann-Fritsch</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Zürcher Kantonal Bank, Innosuisse, Shiloh Advisors, Government of France, The Wyss Foundation</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Lean Team (11-50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>RIVR</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>$25.5M</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Alexander Reske, Giorgio Valsecchi, Lorenz Wellhausen, Marko Bjelonic</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>HSG, Bezos Expeditions, Linear Capital, Agile Robots AG, Innosuisse</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SIX</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CHF250M</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Debt Financing</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Major Organization (1,001-5,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Veezoo</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Veezoo is a search-based self service analytics tool that enables every user to find and visualise new insights from their database - irrespective of their technical skills. With Veezoo, users can be operational from Day One: it only takes a few minutes to connect a new database and get started with...</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>$6.7M</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Joao Pedro Monteiro, Marcos Monteiro, Till Haug</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Tenity, Innosuisse, SICTIC, ACE Ventures, Thomas Dübendorfer</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Founding Team (1-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Loft Dynamics</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>$53.3M</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Fabian Riesen</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Craft Ventures, UP Partners, Sky Dayton, The Friedkin Group, Alaska Star Ventures</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>21Shares</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>$25M</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Hany Rashwan, Ophelia Snyder</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Valor Equity Partners, Morgan Creek Digital, Marshall Wace, Collab+Currency, Anthony Pompliano</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Mid-Size Team (51-250)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>dacadoo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dacadoo.com/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>CHF70M</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Squirro</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>http://squirro.com/</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Squirro is a company founded in 2012 by Dorian Selz, Patrice Neff, Felix Hürlimann and Toni Birrer.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>$15.5M</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Felix Hürlimann</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Beekeeper</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>http://www.beekeeper.io/</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Beekeeper is a provider of digital tools for frontline teams founded in 2012 by Flavio Pfaffhauser, Cris Grossmann and Cristian Grossmann.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>$181.5M</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hitachienergy.com/</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>$24.2M</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GenTwo</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gentwo.com/</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>At GenTwo, we enable financial institutions, asset managers, and advisors to create and scale investment products as easily as booking a flight. We do this through our flagship platforms: GenTwo Pro and the GenTwo Pro AMC Engine.
+In detail:
+We help a) Asset managers and advisors create unique, off-...</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>$15M</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Point72 Ventures</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Steven and Marco</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>DeepJudge</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>https://trydeepjudge.com/</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Law firms, corporations and financial institutions such as banks, insurances and consultancies are producing hundreds of millions of legal documents that sit within their databases. Very frequently a question comes of the sort “Have we done this before?” or “Have we answered this question previously...</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>$11.1M</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Swiss Fintech Awards 2022</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Kevin, Yannic and Florian</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Jua</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jua.ai/</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Jua is building a universal physics simulator tackling weather prediction for energy traders as the first use case.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>$32.9M</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Ananda Impact Ventures</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Andreas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Collabree</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.collabree.com/</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>CHF3.3M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Convertible Note</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PriceHubble</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pricehubble.com/</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>$34M</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Verity</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>https://verity.net/</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>$81M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Ledgy</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ledgy.com/</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Ledgy is a End-to-End equity management platform founded in 2017 by ben brandt, timo horstschaefer and yoko spirig.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>$33.4M</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>ben brandt</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>FE fundinfo</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fefundinfo.com/</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>£3M</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Equity Crowdfunding</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Scandit</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>http://www.scandit.com/</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Scandit is an enterprise barcode scanner founded in 2009.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>$273.1M</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Christian Floerkemeier</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>NGP Capital</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Positrigo</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.positrigo.com/</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>$25M</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Venture Round</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>European Innovation Council</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Araris Biotech</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ararisbiotech.com/</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>$43.4M</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Wingtra</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>https://wingtra.com/</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Wingtra is a company that creates a VTOL drone system for mapping and surveying purposes.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>$43.9M</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Relai</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://relai.app/</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Relai is a crypto trading app founded in 2020 by Julian Liniger.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>$21.8M</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Cerrion</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cerrion.com/</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>AI-driven video agent platform for real-time manufacturing production insights and process anomaly detection.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>$5M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Karim Saleh **@cerrion.com, Michael Gygli</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Y Combinator</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Nikolay</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Yokoy</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://yokoy.io/</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Yokoy is a FinTech company that offers a spend management platform that automates expense, invoicing, and credit card processing.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>$107.8M</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>lars mangelsdorf</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Decentriq</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>https://decentriq.com/</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Decentriq is a company combining machine learning and cryptography to analyze any dataset.</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>$26.2M</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Eclipse Ventures</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Daedalean</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://daedalean.ai/</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Daedalean is building autonomous piloting software systems for civil aircraft of today and advanced aerial mobility of tomorrow.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>$72.5M</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Luuk van Dijk</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Evulpo</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.evulpo.com/</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>$21.7M</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Serpentine Ventures</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ZATAP</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://collectid.io/</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>$3.6M</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Morgen</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>https://morgen.so/</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>CHF1M</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Seed</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Fu-Gen</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fu-gen.com/</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>$320M</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Piomic</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>http://www.piomic.com/</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>CHF10.2M</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TON Provider</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://tonprovider.org/</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>$7.4M</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Tethys Robotics</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>https://tethys-robotics.ch/</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>CHF340k</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Onchain labs</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.onchainlabs.ch/</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>CHF5M</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ETFbook</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etfbook.com/</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>$4M</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>BlackFin Capital Partners</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Microcaps</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.microcaps.ch/</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Biotech</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>CHF14.4M</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Rivia</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rivia.ch/</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>$3M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>rready</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rready.com/</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>$6.3M</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Series A</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>South Pole</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Corporate social responsibility, Consulting industry, Sustainable energy</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>South Pole is a Zurich-based climate solutions company offering sustainable project development services in order to provide carbon offset credits to businesses and organizations.</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Renat Heuberger, Christoph Grobbel</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Starmind.ai</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Software, Software as a service (SaaS), Technology</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Starmind is a Zurich-based software company and provider of AI-powered collaboration platform, founded in 2010.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>$35.0M</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Yttrium (Digital+Partners)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Jenna</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Univerbal</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Speech recognition, Educational Technology, Natural language processing (NLP)</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Univerbal provides a language-learning app with a chatbot AI that simulates the experience of conversing with a foreign speaker.</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>$500.0K</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Teralytics</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Public transport, Big data, Machine learning</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Teralytics is a Zürich-based analytics firm focused on the transportation and mobility sectors, founded in 2012.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>$35.5M</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Luciano Franceschina</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Health technology, Technology, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ava is a women's health company based in Zurich and San Francisco.</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>$77.0M</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Lea von Bidder, Philipp Tholen, Pascal Koenig</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Isovalent</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Software as a service (SaaS), Network security, Cloud management</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Isovalent is a Mountain View, California-headquartered developer of cloud-native networking and security, through the company's Cilium product.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>$69.0M</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Dan Wendlandt ***@isovalent.com</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Anapaya</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Internet, Computer network, Technology</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Anapaya is a Zurich, Switzerland-based private network infrastructure provider and developer of a secure networking protocol separate from and capable of being used with the internet.</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>$21.1M</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Apiax</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Compliance, Legal technology, Information technology</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Apiax transforms complex regulations into digital compliance rules, which are constantly up-to-date and verified, accessible via an API.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>$8.1M</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>FQX</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Digital currency, Finance, Blockchain</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>FQX is radically facilitating trade finance &amp; money markets by using eNotes™</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>$6.7M</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>LatticeFlow</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Machine learning, Artificial Intelligence (AI), Technology</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>LatticeFlow helps organizations build and deploy artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>$29.6M</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Innosuisse - Swiss Agency for Innovation</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Kenjo</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>B2B, Software as a service (SaaS), HR software</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Kenjo is the HR software designed for the modern world.</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>$21.7M</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Anjarium Biosciences</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Therapeutics, Therapy, Drug delivery, Mobility, Electric vehicle, Hardware</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Anjarium is an early-stage biotechnology company developing next-generation, non-viral gene therapy therapeutics.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>$121.0M</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Urban Connect, Urban Connect is an app based booking platform providing access to bikes, e-bikes, e-scooters or e-cars., Judith Häberli</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Software as a service (SaaS), E-commerce</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Mila is a Zurich-based crowd services platform where users can find, book and rate tech-savvy people or offer their technical know-how.</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>$5.2M</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Acodis</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Marketing, Software, Finance</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Acodis is a developer of Intelligent Document Processing (IDP) software, allowing for the digitization of documents.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>$11.5M</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Base 58 Capital</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Blockchain, Hedge fund, Investment</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Base 58 Capital is an hedge fund managing company that specializes in cryptocurrencies and blockchain-based tokens.</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Pexapark AG</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Clean technology, Blockchain and cryptocurrency, Financial technology</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Pexapark AG is a blockchain company founded in 2017 by Michael Waldner, Florian Müller and Luca Pedretti.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>$64.5M</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Seervision AG</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Broadcasting, Machine learning, Computer Vision</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Seervision AG is a Zurich-based software company co-founded in 2016 by Conrad von Grebel, Nikos Kariotoglou, and Reto Hofmann.</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>$7.3M</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Numbrs</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Bank, Mobile Devices, Financial technology</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Platform for managing bank accounts and personal finances.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>$199.2M</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Julien Arnold, Martin Saidler</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>CLST</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Financial technology, Web3</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>CLST is a we create markets for the new money founded in 2021.</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Avon Ventures</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>hugh</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Fotokite</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Unmanned aerial vehicle (UAV), Drones, Public security</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Fotokite is a company that builds drones specifically to assist first responders.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>$20.5M</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Sergei Lupashin</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>MSA Safety</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Chris and Gregory</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Obligate</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Decentralized Finance, Cryptocurrency, Investing</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Obligate Switzerland-based platform created to allow companies to issue on-chain bonds and commercial paper to obtain funding from investors.</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>$15.7M</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>9T Labs</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>3D printing, Aerospace, Manufacturing</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>9T Labs is a carbon composite manufacturing technology developer founded in 2018 by Martin Eichenhofer, Chester Houwink and Giovanni Cavolina.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>$27.8M</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>BC Platforms</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Software, Genetics, Genomics</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>BC Platforms provide data management systems for clinical and genomic research, pharmacogenomics research, preventive and personalized medicine, and biobanking.</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>$44.0M</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Immunai</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Generative AI, Diagnosis, Biotechnology</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensively mapping and reprogramming the immune system with single-cell biology and AI to power new therapeutic discoveries, accelerate drug development and improve patient outcomes</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>$313.0M</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Ansuman Satpathy, Dan Littman</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Moximed</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Biotechnology, Healthcare</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Moximed is a medical equipment manufacturing company that specializes in developing innovative solutions for osteoarthritis</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>$182.8M</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ImmunOs Therapeutics</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Biotechnology, Biomedical engineering, Immunotherapy, Software as a service (SaaS), Finance, Financial technology</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>FinTech, Business Process Solution, SaaS, Accounting, Web App, Mobile App</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>$2.3M</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Stefan Mitrović</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Servoy</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing, Software, Software as a service (SaaS)</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Servoy is a company founded in 2001 by Ron van der Burg.</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Ron van der Burg, Laurens Bushoff</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Locatee</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Analytics, Data analysis, Retail</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Workplace analytics solution that turns data into space utilization insights.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>$16.3M</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Fyrfly Venture Partners</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Clare</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>CareerFairy</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Information technology, College recruiting</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>A company in Switzerland that creates livestreaming between employers and employees for the former to communicate their mission.</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>$1.8M</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>StartAngels Network</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>DeepCode</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Software as a service (SaaS), Cloud computing, User experience design, Information technology, Software as a service (SaaS), Business intelligence (BI)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>deskbird is an AI-driven hybrid workplace management platform founded in 2020 by Ivan Cossu.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>$59.0M</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Veselin Raychev, deskbird</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>OneSoil</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>E-agriculture, Artificial Intelligence (AI), Machine learning</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Platform for agricultural professionals to monitor fields and increase yields.</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>$11.0M</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Neon</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Devices, Finance, Financial technology</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>neon-free is a neobank based in Switzerland offering Personal accounts including a debit card, with all transactions being managed from an iPhone or Android application. neon-free currently accepts to open mobile bank accounts for residents of Switzerland.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>$135.8M</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Spitch</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Speech recognition, Voice recognition, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Platform delivering AI solutions for business communication needs.</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>$3.6M</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Sygnum</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Blockchain and cryptocurrency, Investment, Finance</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>$90.0M</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>OTO Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Customer support, Customer service, Customer success</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Oto is a Zürich, Switzerland-based artificial intelligence company building conversational tech solutions.</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>$16.5M</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Verity Studios</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Computer Vision, Technology, Autonomous System</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Verity Studios has established itself as a provider of drone shows.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>$47.5M</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Lightly</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Computer Vision, Technology, Software as a service (SaaS)</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Lightly is a data curation company for machine learning that helps companies build better models through better data.</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>$3.1M</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Starmind International</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise software, Software as a service (SaaS), Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Starmind connects employees to colleagues with answers through self-learning knowledge networks enabled by AI</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>$25.0M</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Memo Therapeutics</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Biomedical engineering, Drug discovery, Engineering</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Memo Therapeutics is an antibody Discovery Technology founded in 2012.</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>$83.6M</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Nexxiot</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI), Software, Supply chain management</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Nexxiot is a TradeTech pioneer with a mission to enable easier, safer, and cleaner transportation for all stakeholders in the supply chain.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>$103.0M</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Notabene</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Blockchain and cryptocurrency, Insurance, Cryptocurrency</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Notabene builds privacy-preserving compliance tools for financial institutions and crypto companies.</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>$20.8M</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Alice Nawfal, Ania Lipinska</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Advanon</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Financial services, Finance, Financial technology</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Advanon is an online platform where SMEs can find funds for their short-term financing needs by selling invoices to financial investors.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>$110.0K</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Phil Lojacono, Stijn Pieper</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>BRD (formerly breadwallet)</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Cryptocurrency, Virtual currency, Mobile payment</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>The most renowned iPhone bitcoin wallet, including an Android app. Breadwallet allows the users to have complete control over their funds along with security and privacy features. The interface of the wallet is highly appreciated and helps in preventing bitcoin theft.</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Voisine</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Embotech</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Automotive industry, Aerospace, Information Technology &amp; Services</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Provider of autonomous driving solutions for industrial logistics applications.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>$11.0M</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>IRsweep</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Healthcare, Aerospace</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>IRSweep is a technology research and developing company.</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>$141.3K</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Crypto Storage AG</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Asset management, Technology, Financial services, Cryptocurrency, Blockchain, Financial services</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>flov technologies is a privately owned financial services company.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>$39.4M</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>flov technologies, Emanuel Burgener</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Uepaa AG</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Software, Technology, Security, Social commerce, E-commerce, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>guuru is a platform providing AI-powered customer service founded in 2015.</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>$10.4M</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Franck Legendre, guuru</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Xapo</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Cryptocurrency wallet, Blockchain, Finance</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Xapo is a Zürich-based company founded in 2013 by Wences Casares.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>$23.0M</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Wences Casares (entrepreneur)</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Cradle</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Technology, Generative AI, Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Cradle is an AI-powered protein engineering platform founded in 2021 by Stef van Grieken , Elise de Reus and Eli Bixby.</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>$102.7M</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>Eli Bixby ***@cradle.bio</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Mirai Foods</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Biology, Cellular agriculture, Plant-based meat</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Mirai Foods is a plant-based company producing real meat from animal stem cells.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>$6.7M</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Sign up to access our full database, Enter your email and get access to 71,000 + technology companies you can partner with., Access 71k+ startups</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Oviva</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Oviva is digitising dietetics to help people with chronic conditions related to diet and lifestyle learn how to better self-manage and improve their health. Our mission is to revolutionise access and outcomes for dietetics.
+We convert traditional face-to-face dietetic care into digital programmes s...</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>Norrsken VC</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>Kai, Manuel and Mark</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Molecular Partners</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Medixci</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Flexion Robotics</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>DST Global</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Boost inc</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Kineo finance</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Pascal</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Voliro AG</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>Loris</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Gravis Robotics</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>A/O PropTech UK</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>BURAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Swiss-Mile</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>Linear Capital</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Mimic Robotics</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>$169.5k</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Venture Kick</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>https://unique.ch</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>FSI companies face inefficient processes and financial pressures, requiring AI assistants to overcome high costs. In most companies today, traditional research methods and human expertise are relied upon to analyze data, make decisions, and address customer inquiries. Access to information is limite...</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Andreas Hauri</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>Lea</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Zitadel</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Zitadel is modernizing the Identity and Access Management (IAM) category by focusing on developer-first, open source identity infrastructure designed for modern multi-tenant, cloud-native applications. In a market traditionally dominated by complex enterprise solutions, Zitadel brings simplicity and...</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>$2.5m</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Nexus Venture Partners</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Swarna</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Deskbird</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>Session.vc</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SkyCell</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>$57m</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;G Catalyst</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>embotech AG</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Embotech is a leading developer of cutting-edge decision-making solutions for real-time applications. Our embeddable software empowers autonomous systems to make decisions by solving complex optimization problems in milliseconds, bringing significant improvements in safety, flexibility, productivity...</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Yttrium (Digital+Partners)</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>George and Juan</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Ahead Health</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Pareto Holdings</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Almanak</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Shima Capital</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>LocalStack</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Heavybit</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Tethys Robotics - Switzerland</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Tethys Robotics automates underwater infrastructure inspections by developing
+autonomous and compact robotic solutions designed to operate in the most challenging water conditions.
+By integrating advanced sensor technologies, AI-driven mapping, and durable engineering, we enable efficient, safe, an...</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>$2</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>Jonas and Ana</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Calvin Risk</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>AI adoption is growing rapidly, but its deployment often faces significant risks and challenges. Organizations struggle with understanding, managing, and mitigating the risks posed by AI systems, such as bias, safety issues, and regulatory non-compliance.
+Current processes for AI risk assessment ar...</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>FinTech Innovation Lab</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Anastasia</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Metafuels</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>$4.9m</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>Swiss Federal Office of Energy</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Porters</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Seedcamp (SC)</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Turtle</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>https://turtle.xyz</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>GSR Ventures</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>EvlaBio</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Kurma Partners</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Wenzel</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Food Brewer</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>Lindt &amp; Sprüngli</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Lightium</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>$3.1m</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Innosuisse - Swiss Agency for Innovation</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>CUE</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>https://cuelang.org</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>Dell Technologies Capital</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Haelixa</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Zürcher Kantonalbank</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Gediminas</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>a-metal</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>$214.4k</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>ESA BIC Switzerland</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Scalera</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>BfW - Bank</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Somagenetix</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>VI Partners AG</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Enso Finance</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Bodhi Ventures</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Optiml Ag</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>$11.3k</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>Venture Kick</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>Nico</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Centi AG</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Payment infrastructure running on a highly performant blockchain; making payments much cheaper but allowing clients to stay in their used web2 environments</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>$1.6m</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Archblock</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Bernhard, Ralf and Valon</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Lakera</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>Dropbox Ventures</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>David and Matthias</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Nautica Technologies</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>b2venture</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>ZuriQ</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>QAI Ventures</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Everyman Health</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Joyned Capital</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Apheros</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Apheros tackles a the most critical challenge in high-performance computing (HPC): cooling. Apheros' innovative metal foams offer superior heat transfer, excellent flow properties, and high compatibility with existing liquid cooling systems. The foams provide 1000x the surface area of competitors' p...</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>$2m</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Founderful</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Schuman Financial AG</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>MVP is launching this autumn. Major European Exchanges are already onboard.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>$3.4m</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Faction VC</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Selma Finance AG</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>For people who want to grow their wealth and make sure their financial future is secured in the best way – but don’t know how – Selma is the digital financial advisor that makes investing and financial planning easy and effortless.
+Selma manages your money automatically, gives personalized advice &amp;...</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Swiss Fintech Awards 2024</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>Patrik Oliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>tiun.</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>tiun. was founded in 2023 as a Swiss B2B2C fintech company based in Zurich.
+Our journey started with a simple idea: enabling the next generation to connect their mobile wallets to any application and pay only for the time they consume—much like SBB EasyRide, but for any app.
+Our mission is to esta...</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Fintech Awards 2025</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Sandro, Christian and Nikolaos</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Wyden</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Wyden is the global leader in institutional digital asset trading technology. By covering the entire trade lifecycle and supporting seamless custody, core banking and portfolio management system integration as well as full trade lifecycle automation, the Wyden platform streamlines digital assets tra...</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>Block.one (B1)</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>Anders</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Unisers</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Swisscom Ventures</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Calingo Insurance AG</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>We are convinced that insurance must become radically simple to provide maximum customer convenience. This includes fair products, uncomplicated distribution channels, and a digital offering. And that's exactly what Calingo does. Thanks to our positioning at the Point of Need and based on the data a...</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>$1.8m</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>Swiss ICT Investor Club (SICTIC)</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>Marlo, Daniel and Anina</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Swissport</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>King Street Capital</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Suzannah, Steven and Kyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Qala AG</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>Swiss ICT Investor Club (SICTIC)</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Chipmind</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Wingman Ventures</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Nextesy</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>SICTIC Startup Application</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Taskbase</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>$1.5m</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Swiss ICT Investor Club (SICTIC)</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Avrios</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Founded in 2015, Avrios is the first fully digital vehicle fleet manager and one of the fastest growing startups in Zurich. We currently have over 600 clients including world leaders in sports goods, drinks, pharma and consulting. The Avrios web-based platform stands for mobility and helps our custo...</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Edenred Capital Partners</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>Andreas, Kathryn and Wouter</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Zenline AI</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Seedcamp (SC)</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>sallea</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>Founderful</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Cellvie</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>$5m</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Kizoo</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>TONI Digital</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>The Swiss insurance market is expensive, complex, and slow to innovate. Customers demand simpler, more affordable, and digital-first solutions—but traditional insurers struggle to deliver.
+At Toni Digital, we change this by offering cost-effective, white-label insurance solutions seamlessly embedde...</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>$47.5m</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>Various Companies</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>Bernard, Tobias and Karla</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>ABB Robotics</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Emilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Loki Robotics, Inc</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>byFounders</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Sunrise GmbH</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Modulos AG</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>Simone and Elena</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Oxyle AG</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>The Swiss Solution to a Global Problem​. We protect our precious water resources, humans, and our environment from the negative impacts of highly persistent, mobile and toxic micropollutants with our efficient and sustainable technology.
+Micropollutants represent a massive range of organic pollutan...</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>SOSV</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Silvan and Fajer</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>neon Switzerland</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Excessive fees, inflexible opening times, too much bureaucracy and complicated, slow apps. To us, it was clear: it can’t go on like that. That’s why we built neon.
+neon is an account on your smartphone, the way we want it to be. Super cheap - no base fees. Fast and independent. Mobile without limit...</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>Schwyzer Kantonalbank</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>Jörg and Simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Fruitful AI</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Hatteland Group</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>SIX Group</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>finance stuff</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>Claudia and Haya</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ABB Group</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Giuseppe and Stephane</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>CrowdSports</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>CrowdSport provides a platform where football fans can participate in funding and shaping their favorite clubs and earning financial rewards based on club performance, along with unique personal experiences.
+The business model is coordinated with FIFA and meets all financial regulatory requirements,...</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>Move+ scale</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>Leroy, Romeo and Roger</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Flink Robotics</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>$167.2k</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Venture Kick</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Calico Biosystems</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>$167.2k</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>Venture Kick</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>vlot Ltd</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Swiss InsurTech Hub Awards '23</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Sandro and Daniel</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Sleepiz</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Sleepiz AG (Ltd.) is a Zürich based startup with the aim to enable the medical community to take healthcare into the home environment. Sleepiz provides a comfortable and easy to use solution with a device that is simply placed on the bedside table. The device operates in a non-contact fashion and me...</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>Höhle der Löwen Schweiz</t>
+        </is>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>Soumya</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Zürcher Kantonalbank</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>Andri and Simon</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Zurich Insurance Group.</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>Warren, Thomas and Marine</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Akina</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>https://akina.health</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>$3.2m</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Freigeist Capital</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>SERA Intelligence</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>SERA is an AgTech company that offers a cultivation management &amp; data analytics platform for greenhouses using machine learning.</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>Cavalry Ventures</t>
+        </is>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Healactively</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Unspecific back pain is a condition affecting 630 million people worldwide, 72 million in the US, 92 million in Europe, and 2.4 million in Switzerland and is fast growing due to sedentary lifestyles, obesity, tobacco (...) . It is the leading cause of disability worldwide.
+Our purpose is to make li...</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>$94.9k</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>Mathieu Stremsdoerfer</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Mathieu, Daniel and Liz</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Glimpse Health</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>At Glimpse Health, we aim to develop state-of-the-art digital biomarkers and establish them as the new gold standard for fatigue quantification. Our idea is to support pharmaceutical companies in demonstrating the efficacy of fatigue treatments. Long-term, we want to use our biomarkers to help patie...</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>$192.1k</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>Universität Zürich | University of Zurich</t>
+        </is>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>Pietro and Liliana</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Farmy Switzerland</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Farmy is a food tech company.
+Farmy is the No. 1 online market place in Switzerland for sustainable grocery shopping, connecting more than 1000 regional and sustainable food makers with end customers.
+Farmy disrupts by bypassing the wholesale and delivering with e-vans. Like this we eliminate food w...</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Tomahawk.VC</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Tobias and Roman</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>delta.network</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>Credibly Neutral</t>
+        </is>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Napkin</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>https://napkin.one</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Exnaton</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Our software “EnergyCommunity” empowers electricity providers to set up energy communities in their distribution areas. Households can directly buy renewable electricity from their neighbors (from ‘peer to peer’) on the EnergyCommunity platform and can track their environmental impact with the Energ...</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>True Ventures</t>
+        </is>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>Arne, Liliane and Anselma</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Way Ahead Technologies AG</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Making driving safer, more efficient and more entertaining - real-time AR and 3D experiences in the vehicle and beyond.
+Based on computer vision, we build highly precise AR-Technology, allowing us to place virtual content into driving cars through heads up displays or AR glasses.
+Way Ahead Technol...</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Roger and Michael</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Timly Software AG</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Timly Inventory is a cloud-based asset tracking, management and automation tool to track the activities around a wide variety of physical assets.
+When a CRM helps companies manage all activities around clients, Timly tracks all activities around your inventory. Timly provides companies with an over...</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>Philipp and Fitim</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Gimme - Ordering &amp; Payment</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Gimme is a platform that dramatically reduces lines, transform the guest experience and see that all important boost in sales. Guests can order, reorder and pay with Gimme. Without the need to download an app. 📱
+We want to save your guest's time and not wait in line. Social is our sauce. With gamif...</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Goran</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>FundFirms</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>FundFirms is a blockchain integrated SME investment platform that leverages DeFi in order to connect real-world firms with a global network of investors throughout the blockchain, while minimizing restrictions that would otherwise hinder capital mobility, creating a truly global and efficient invest...</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>Vit and Dennis William</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Circular Flow Technologies</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>We provide a technology that treats and concentrates wastewater on-site at the bathroom scale to produce a dry pathogen-free fertilizer product. We transform the bathroom from a waste emission towards a fertilizer production site using our innovative on-site treatment technology.
+Our first product ...</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>Venture Kick</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Michel and Kai</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J176"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>